--- a/SGC-CKN/Excel/50fa0016-aedf-430f-99b4-769101396a72_Cọc_khoan_nhồi_P7_D800_12-04-2026.xlsx
+++ b/SGC-CKN/Excel/50fa0016-aedf-430f-99b4-769101396a72_Cọc_khoan_nhồi_P7_D800_12-04-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7</t>
+    <t>P7-72</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/50fa0016-aedf-430f-99b4-769101396a72_Cọc_khoan_nhồi_P7_D800_12-04-2026.xlsx
+++ b/SGC-CKN/Excel/50fa0016-aedf-430f-99b4-769101396a72_Cọc_khoan_nhồi_P7_D800_12-04-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="80">
   <si>
     <t>Dự án</t>
   </si>
@@ -163,11 +163,11 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">04:43
+    <t xml:space="preserve">01:43
 12/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">04:29
+    <t xml:space="preserve">02:29
 12/04/2026</t>
   </si>
   <si>
@@ -192,6 +192,10 @@
   </si>
   <si>
     <t xml:space="preserve">04:09
+12/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:29
 12/04/2026</t>
   </si>
   <si>
@@ -330,12 +334,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <color rgb="FF365314"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -357,6 +355,12 @@
     </font>
     <font>
       <color rgb="FF134E4A"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
@@ -432,11 +436,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD9F99D"/>
       </patternFill>
     </fill>
@@ -458,6 +457,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -621,6 +625,12 @@
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -659,12 +669,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1404,196 +1408,196 @@
         <v>-26.15</v>
       </c>
       <c r="H15" s="19">
-        <v>23.77</v>
+        <v>0.77</v>
       </c>
       <c r="I15" s="19">
         <v>4.7</v>
       </c>
-      <c r="J15" s="22">
-        <v>0.2</v>
+      <c r="J15" s="8">
+        <v>6.13</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="22">
         <v>-26.15</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>-36.1</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>1.63</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="22">
         <v>9.95</v>
       </c>
       <c r="J16" s="8">
         <v>6.09</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="E17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="E17" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F17" s="25">
         <v>-36.1</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="25">
         <v>-38.5</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="25">
         <v>0.33</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="25">
         <v>2.4</v>
       </c>
       <c r="J17" s="8">
         <v>7.2</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K17" s="26" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="31" t="s">
+      <c r="C18" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="D18" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="29">
+      <c r="E18" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="28">
         <v>-38.5</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>-40</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.3</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="28">
         <v>1.5</v>
       </c>
       <c r="J18" s="12">
         <v>5</v>
       </c>
-      <c r="K18" s="30" t="s">
+      <c r="K18" s="29" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" s="32" t="s">
+      <c r="A19" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="34" t="s">
+      <c r="C19" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="D19" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="32">
+      <c r="E19" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="31">
         <v>-40</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="31">
         <v>-44</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="31">
         <v>1.1</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="31">
         <v>4</v>
       </c>
       <c r="J19" s="12">
         <v>3.64</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="32" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="35" t="s">
+      <c r="A20" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="D20" s="36" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="35">
+      <c r="E20" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="34">
         <v>-44</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <v>-44.65</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <v>0.65</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>0.65</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="37">
         <v>1</v>
       </c>
-      <c r="K20" s="36" t="s">
-        <v>68</v>
+      <c r="K20" s="35" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1699,31 +1703,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1862,38 +1866,38 @@
         <v>-26.15</v>
       </c>
       <c r="G6" s="19">
-        <v>23.77</v>
+        <v>0.77</v>
       </c>
       <c r="H6" s="19">
         <v>4.7</v>
       </c>
-      <c r="I6" s="22">
-        <v>0.2</v>
+      <c r="I6" s="8">
+        <v>6.13</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>1</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>-26.15</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>-36.1</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>1.63</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>9.95</v>
       </c>
       <c r="I7" s="8">
@@ -1901,28 +1905,28 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>1</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="25">
         <v>-36.1</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="25">
         <v>-38.5</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="25">
         <v>0.33</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="25">
         <v>2.4</v>
       </c>
       <c r="I8" s="8">
@@ -1930,28 +1934,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="29">
+      <c r="C9" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="28">
         <v>-38.5</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>-40</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0.3</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>1.5</v>
       </c>
       <c r="I9" s="12">
@@ -1959,28 +1963,28 @@
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="32">
+      <c r="C10" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="31">
         <v>1</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <v>-40</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-44</v>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <v>1.1</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>4</v>
       </c>
       <c r="I10" s="12">
@@ -1988,37 +1992,37 @@
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+      <c r="A11" s="34">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
+      <c r="B11" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="35">
+      <c r="C11" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="34">
         <v>1</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <v>-44</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <v>-44.65</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="34">
         <v>0.65</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <v>0.65</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="37">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2036,13 +2040,13 @@
         <v>-44.65</v>
       </c>
       <c r="G12" s="40">
-        <v>33.63</v>
+        <v>10.63</v>
       </c>
       <c r="H12" s="40">
         <v>43.8</v>
       </c>
       <c r="I12" s="40">
-        <v>1.3</v>
+        <v>4.12</v>
       </c>
     </row>
   </sheetData>
